--- a/Q4_0/Assumption1_Params.xlsx
+++ b/Q4_0/Assumption1_Params.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="2">
   <si>
     <t>FirstSplitIndex</t>
   </si>
@@ -81,10 +81,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>8735</v>
+        <v>6313</v>
       </c>
       <c r="B2" s="0">
-        <v>87340</v>
+        <v>63120</v>
       </c>
     </row>
   </sheetData>
